--- a/data/seed/portfolio/L-2025-6825/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-6825/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J194"/>
+  <dimension ref="A1:J184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,282 +535,282 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>5375000</v>
+        <v>6834000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №270/26 от 01.07.2026</t>
+          <t>Оплата за продукцию по дог. №256/26, НДС 12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>35075000</v>
+        <v>36534000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>4524000</v>
+        <v>2071000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №927 за поставленный товар</t>
+          <t>Оплата по с/ф №1432 за поставленный товар</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>39599000</v>
+        <v>38605000</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B10" t="n">
         <v>102</v>
       </c>
       <c r="C10" s="2" t="n"/>
       <c r="D10" s="2" t="n">
-        <v>602000</v>
+        <v>2713000</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8474 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №7681 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>40201000</v>
+        <v>41318000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>13794000</v>
+        <v>1600000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №9452 за поставленный товар</t>
+          <t>Shartnoma №32/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>53995000</v>
+        <v>42918000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="n">
-        <v>2123000</v>
-      </c>
-      <c r="D12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n">
+        <v>1416000</v>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №1552</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №180/26 ОТ 06.07.2026</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>51872000</v>
+        <v>44334000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>1129000</v>
+        <v>1244000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tong Non MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>355228810</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000706960004001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №92/26, QQS 12%</t>
+          <t>Оплата за товар по счет-фактуре №204 от 06.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>53001000</v>
+        <v>45578000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>548000</v>
+        <v>903000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №292/26, НДС 12%</t>
+          <t>Оплата за продукцию по дог. №204/26, НДС 12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>53549000</v>
+        <v>46481000</v>
       </c>
     </row>
     <row r="15">
@@ -822,35 +822,35 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>19216000</v>
+        <v>852000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №673 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №218/26, НДС 12%</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>72765000</v>
+        <v>47333000</v>
       </c>
     </row>
     <row r="16">
@@ -860,37 +860,37 @@
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>8439000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>6032000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №7757 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №2653</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>81204000</v>
+        <v>41301000</v>
       </c>
     </row>
     <row r="17">
@@ -900,1578 +900,1573 @@
       <c r="B17" t="n">
         <v>109</v>
       </c>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n">
-        <v>7310000</v>
-      </c>
+      <c r="C17" s="2" t="n">
+        <v>10798000</v>
+      </c>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>379461924</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2500 за поставленный товар</t>
+          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>88514000</v>
+        <v>30503000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n"/>
       <c r="D18" s="2" t="n">
-        <v>5240000</v>
+        <v>5625000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Gulshan Meva Eksport MChJ</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>223968561</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000359205594001</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №6365 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товар по счет-фактуре №1729 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>93754000</v>
+        <v>36128000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n">
-        <v>1179000</v>
+        <v>2821000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9562 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №9220 от 07.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>94933000</v>
+        <v>38949000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
-      <c r="C20" s="2" t="n">
-        <v>2214000</v>
-      </c>
-      <c r="D20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n">
+        <v>2097000</v>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №833</t>
+          <t>Оплата по с/ф №3787 за поставленный товар</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>92719000</v>
+        <v>41046000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>10798000</v>
+        <v>1092000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Shahrisabz Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>387683548</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000759953911001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Заработная плата за июнь 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Арендная плата за июль 2026 г. по договору №51/25</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>81921000</v>
+        <v>39954000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>688000</v>
+        <v>4964000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7254 от 07.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №5778 от 09.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>82609000</v>
+        <v>44918000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>2998000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>13422000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saodat Dori-Darmon XK</t>
+          <t>Namangan Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>214547449</t>
+          <t>232722302</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000670863096001</t>
+          <t>20208000251961831001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №9704</t>
+          <t>Оплата за товар по счет-фактуре №134 от 13.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>79611000</v>
+        <v>58340000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46210</v>
+        <v>46216</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>12375000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>5755000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №96/26</t>
+          <t>Оплата по счет-фактуре №9620 за поставленный товар</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>67236000</v>
+        <v>64095000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46211</v>
+        <v>46216</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>3275000</v>
+        <v>1962000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>370754710</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000693120780001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8614 08.07.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №4038 за поставленный товар</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>70511000</v>
+        <v>66057000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n"/>
       <c r="D26" s="2" t="n">
-        <v>6717000</v>
+        <v>1958000</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5853 от 09.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за продукцию по договору №81/26, НДС 12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>77228000</v>
+        <v>68015000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n"/>
       <c r="D27" s="2" t="n">
-        <v>622000</v>
+        <v>1918000</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Qo'qon Polimer MChJ</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>296725554</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000513130573001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1958 за поставленный товар</t>
+          <t>Tovar uchun to'lov, h/f №6189 13.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>77850000</v>
+        <v>69933000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46212</v>
+        <v>46218</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n">
-        <v>1092000</v>
-      </c>
-      <c r="D28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n">
+        <v>4090000</v>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>389270245</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000515169628001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Аренда помещения за июль, дог. №85/23</t>
+          <t>Mahsulot uchun to'lov, shartnoma №266/26, QQS 12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>76758000</v>
+        <v>74023000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>1573000</v>
+        <v>2625000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №232/26 от 10.07.2026</t>
+          <t>Оплата по счет-фактуре №942 за поставленный товар</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>78331000</v>
+        <v>76648000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46213</v>
+        <v>46218</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n"/>
       <c r="D30" s="2" t="n">
-        <v>719000</v>
+        <v>866000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tong Non MChJ</t>
+          <t>Bunyodkor Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>355228810</t>
+          <t>328267201</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000706960004001</t>
+          <t>20208000318546732001</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8674 от 10.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №287/26 от 15.07.2026</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>79050000</v>
+        <v>77514000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46213</v>
+        <v>46219</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n">
-        <v>3726000</v>
-      </c>
-      <c r="D31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n">
+        <v>5213000</v>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Namangan Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>232722302</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000251961831001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №1876</t>
+          <t>Предоплата за товар по договору №151/26 от 16.07.2026</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>75324000</v>
+        <v>82727000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>5141000</v>
+        <v>2043000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7876 за поставленный товар</t>
+          <t>Оплата за продукцию по дог. №169/26, НДС 12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>80465000</v>
+        <v>84770000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>1916000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>1472000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №987 за поставленный товар</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>82381000</v>
+        <v>83298000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n">
-        <v>1815000</v>
-      </c>
+      <c r="C34" s="2" t="n">
+        <v>1472000</v>
+      </c>
+      <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №241/26 от 13.07.2026</t>
+          <t>НДФЛ за июнь 2026</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>84196000</v>
+        <v>81826000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n"/>
-      <c r="D35" s="2" t="n">
-        <v>1614000</v>
-      </c>
+      <c r="C35" s="2" t="n">
+        <v>7118000</v>
+      </c>
+      <c r="D35" s="2" t="n"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Andijon Agro MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>261711878</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000751559415001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №128/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №279/26</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>85810000</v>
+        <v>74708000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>1432000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>22804000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №32/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №214/26</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>87242000</v>
+        <v>51904000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>791000</v>
+        <v>3170000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №996 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №8261 17.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>88033000</v>
+        <v>55074000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
       <c r="C38" s="2" t="n"/>
       <c r="D38" s="2" t="n">
-        <v>768000</v>
+        <v>2282000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Sarbon Moy MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>272329434</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000700912752001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5326 от 14.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №635 от 17.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>88801000</v>
+        <v>57356000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5404000</v>
+        <v>8895000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Jizzax Un Mahsulotlari MChJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>346612418</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000418784476001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №82/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №5830</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>83397000</v>
+        <v>48461000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46217</v>
+        <v>46220</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>8276000</v>
+        <v>12247000</v>
       </c>
       <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №8751</t>
+          <t>Оплата за сырье по договору №295/26 от 17.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>75121000</v>
+        <v>36214000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
       <c r="C41" s="2" t="n"/>
       <c r="D41" s="2" t="n">
-        <v>746000</v>
+        <v>18702000</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №12/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №79/26, НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>75867000</v>
+        <v>54916000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
-      <c r="C42" s="2" t="n">
-        <v>1472000</v>
-      </c>
-      <c r="D42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n">
+        <v>4736000</v>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Социальный налог за июнь 2026 г.</t>
+          <t>Оплата за товар по с/ф №722 от 20.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>74395000</v>
+        <v>59652000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n">
-        <v>1472000</v>
-      </c>
-      <c r="D43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="2" t="n">
+        <v>3678000</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Оплата по с/ф №8218 за поставленный товар</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>72923000</v>
+        <v>63330000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46218</v>
+        <v>46223</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>3144000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>2221000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Farovon Farm Savdo MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>308653986</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000294169456001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №2450</t>
+          <t>Оплата за продукцию по дог. №290/26, НДС 12%</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>69779000</v>
+        <v>65551000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
       <c r="C45" s="2" t="n"/>
       <c r="D45" s="2" t="n">
-        <v>1183000</v>
+        <v>1344000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №143/26 от 16.07.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9230</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>70962000</v>
+        <v>66895000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
       <c r="C46" s="2" t="n"/>
       <c r="D46" s="2" t="n">
-        <v>563000</v>
+        <v>1001000</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3989 16.07.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №67/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>71525000</v>
+        <v>67896000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n">
-        <v>2922000</v>
-      </c>
+      <c r="C47" s="2" t="n">
+        <v>6511000</v>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГ. №111/26 ОТ 17.07.2026</t>
+          <t>Оплата за сырье по договору №284/26 от 20.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>74447000</v>
+        <v>61385000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>1199000</v>
+        <v>13059000</v>
       </c>
       <c r="D48" s="2" t="n"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №263/26</t>
+          <t>Предоплата за материалы по дог. №283/26</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>73248000</v>
+        <v>48326000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>1296000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>14519000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Farovon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>268551631</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000220509016001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №134/26 от 20.07.2026</t>
+          <t>Tovarlar uchun to'lov h/f №4032</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>74544000</v>
+        <v>33807000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n">
-        <v>807000</v>
-      </c>
+      <c r="C50" s="2" t="n">
+        <v>3215000</v>
+      </c>
+      <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Mehnat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>291768256</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000543730588001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4576 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №155/26</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>75351000</v>
+        <v>30592000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n"/>
-      <c r="D51" s="2" t="n">
-        <v>1191000</v>
-      </c>
+      <c r="C51" s="2" t="n">
+        <v>22109000</v>
+      </c>
+      <c r="D51" s="2" t="n"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №289/26, НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №286/26</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>76542000</v>
+        <v>8483000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>1175000</v>
+        <v>1643000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №6091 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Предоплата за товар по договору №13/26 от 23.07.2026</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>77717000</v>
+        <v>10126000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1777000</v>
+        <v>1836000</v>
       </c>
       <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Saodat Dori-Darmon XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>214547449</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000670863096001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №54/26</t>
+          <t>Уплата налога на добавленную стоимость за июнь</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>75940000</v>
+        <v>8290000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
-      <c r="C54" s="2" t="n">
-        <v>2957000</v>
-      </c>
-      <c r="D54" s="2" t="n"/>
+      <c r="C54" s="2" t="n"/>
+      <c r="D54" s="2" t="n">
+        <v>4339000</v>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №156/26, QQS bilan</t>
+          <t>Оплата по счет-фактуре №2500 за поставленный товар</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>72983000</v>
+        <v>12629000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n">
-        <v>1713000</v>
-      </c>
-      <c r="D55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n">
+        <v>3749000</v>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июнь</t>
+          <t>Оплата за товар по с/ф №7614 от 24.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>71270000</v>
+        <v>16378000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46226</v>
+        <v>46228</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
-      <c r="C56" s="2" t="n"/>
-      <c r="D56" s="2" t="n">
-        <v>577000</v>
-      </c>
+      <c r="C56" s="2" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>346293251</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-6825)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>16307000257461212417</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2481,552 +2476,552 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №251/26 от 23.07.2026</t>
+          <t>Kredit shartnomasi L-2025-6825 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>71847000</v>
+        <v>978000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>2453000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>1497000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №187/26, QQS bilan</t>
+          <t>Shartnoma №74/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>69394000</v>
+        <v>2475000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
-      <c r="C58" s="2" t="n">
-        <v>7484000</v>
-      </c>
-      <c r="D58" s="2" t="n"/>
+      <c r="C58" s="2" t="n"/>
+      <c r="D58" s="2" t="n">
+        <v>1367000</v>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №127/26</t>
+          <t>Предоплата за товар по дог. №130/26 от 27.07.2026</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>61910000</v>
+        <v>3842000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n"/>
       <c r="D59" s="2" t="n">
-        <v>6441000</v>
+        <v>1086000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Navoiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>254744906</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000086309617001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №37/26 от 24.07.2026</t>
+          <t>Оплата за продукцию по договору №268/26, НДС 12%</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>68351000</v>
+        <v>4928000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n"/>
-      <c r="D60" s="2" t="n">
-        <v>5096000</v>
-      </c>
+      <c r="C60" s="2" t="n">
+        <v>682000</v>
+      </c>
+      <c r="D60" s="2" t="n"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Tong Trans Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>343723294</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000417009127001</t>
+          <t>20208000005529105001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>SHARTNOMA №31/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за электроэнергию за июль 2026 г.</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>73447000</v>
+        <v>4246000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>574000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>5439000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8120 за поставленный товар</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №222/26</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>74021000</v>
+        <v>-1193000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n">
-        <v>682000</v>
-      </c>
-      <c r="D62" s="2" t="n"/>
+      <c r="C62" s="2" t="n"/>
+      <c r="D62" s="2" t="n">
+        <v>15017000</v>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000709052368001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Shartnoma №17/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>73339000</v>
+        <v>13824000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n">
-        <v>1789000</v>
-      </c>
-      <c r="D63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n">
+        <v>6967000</v>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saodat Dori-Darmon XK</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>214547449</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000670863096001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №3362</t>
+          <t>SHARTNOMA №91/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>71550000</v>
+        <v>20791000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>2284000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>3631000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №923</t>
+          <t>Предоплата за товар по договору №187/26 от 29.07.2026</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>69266000</v>
+        <v>24422000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46228</v>
+        <v>46232</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n">
-        <v>15400000</v>
-      </c>
-      <c r="D65" s="2" t="n"/>
+      <c r="C65" s="2" t="n"/>
+      <c r="D65" s="2" t="n">
+        <v>1224000</v>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-6825)</t>
+          <t>Angren Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>16307000257461212417</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-6825 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Предоплата за товар по договору №144/26 от 29.07.2026</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>53866000</v>
+        <v>25646000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>10912000</v>
+        <v>2331000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3550 за поставленный товар</t>
+          <t>Оплата за товар по с/ф №4837 от 30.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>64778000</v>
+        <v>27977000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>2148000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>379461924</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №221 27.07.2026, QQS bilan</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>66926000</v>
+        <v>27677000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>1246000</v>
+        <v>6228000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Navro'z Mebel MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>249958413</t>
+          <t>296856123</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000576803210001</t>
+          <t>20208000920559413001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1816 27.07.2026, QQS bilan</t>
+          <t>Shartnoma №156/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>68172000</v>
+        <v>33905000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n"/>
       <c r="D69" s="2" t="n">
-        <v>954000</v>
+        <v>1456000</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №912 за поставленный товар</t>
+          <t>Shartnoma №31/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>69126000</v>
+        <v>35361000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>1393000</v>
+        <v>1441000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Tong Non MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>355228810</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000706960004001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3036,277 +3031,272 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №9495 от 29.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktra №8066 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>70519000</v>
+        <v>36802000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n">
-        <v>3512000</v>
-      </c>
-      <c r="D71" s="2" t="n"/>
+      <c r="C71" s="2" t="n"/>
+      <c r="D71" s="2" t="n">
+        <v>971000</v>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №255/26</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8739 ОТ 03.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>67007000</v>
+        <v>37773000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
       <c r="C72" s="2" t="n"/>
       <c r="D72" s="2" t="n">
-        <v>2968000</v>
+        <v>971000</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis MChJ</t>
+          <t>Nurafshon Sut MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>370754710</t>
+          <t>330950664</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000693120780001</t>
+          <t>20208000206012374001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №155/26 от 30.07.2026</t>
+          <t>Оплата по счет-фактуре №5539 за поставленный товар</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>69975000</v>
+        <v>38744000</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B73" t="n">
         <v>165</v>
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>1451000</v>
+        <v>826000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №92/26, QQS 12%</t>
+          <t>Yetkazilgan tovar uchunto'lov h/f №2988</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>71426000</v>
+        <v>39570000</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46233</v>
+        <v>46239</v>
       </c>
       <c r="B74" t="n">
         <v>166</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>1921000</v>
+        <v>11805000</v>
       </c>
       <c r="D74" s="2" t="n"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och XK</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>390109711</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>20208000116483821001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №148/26</t>
+          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>69505000</v>
+        <v>27765000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46233</v>
+        <v>46241</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n">
-        <v>4618000</v>
-      </c>
-      <c r="D75" s="2" t="n"/>
+      <c r="C75" s="2" t="n"/>
+      <c r="D75" s="2" t="n">
+        <v>1371000</v>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6627</t>
+          <t>Оплата за товар по счет-фактуре №1825 от 07.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>64887000</v>
+        <v>29136000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46233</v>
+        <v>46241</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>40102000</v>
+        <v>1193000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Jizzax Un Mahsulotlari MChJ</t>
+          <t>Shahrisabz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>346612418</t>
+          <t>387683548</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000418784476001</t>
+          <t>20208000759953911001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №187/26 от 30.07.2026, НДС 12%</t>
+          <t>Арендная плата за август 2026 г. по дог. №51/25</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>24785000</v>
+        <v>27943000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
       <c r="C77" s="2" t="n"/>
       <c r="D77" s="2" t="n">
-        <v>4703000</v>
+        <v>8742000</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3316,112 +3306,117 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №6541 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №166/26, НДС 12%</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>29488000</v>
+        <v>36685000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
-      <c r="C78" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D78" s="2" t="n"/>
+      <c r="C78" s="2" t="n"/>
+      <c r="D78" s="2" t="n">
+        <v>1312000</v>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Angren Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
+          <t>Предоплата за товар по договору №56/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>29188000</v>
+        <v>37997000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n">
-        <v>4326000</v>
-      </c>
-      <c r="D79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n">
+        <v>814000</v>
+      </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Jizzax Un Mahsulotlari MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>346612418</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000418784476001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №164/26</t>
+          <t>Предоплата за товар по договору №268/26 от 10.08.2026</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>24862000</v>
+        <v>38811000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>5989000</v>
+        <v>19201000</v>
       </c>
       <c r="D80" s="2" t="n"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Mehnat Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>291768256</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000543730588001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3431,1472 +3426,1472 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №84/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №5635</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>18873000</v>
+        <v>19610000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
       <c r="C81" s="2" t="n"/>
       <c r="D81" s="2" t="n">
-        <v>4988000</v>
+        <v>13532000</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Shartnoma №151/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №212/26 от 11.08.2026</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>23861000</v>
+        <v>33142000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>2539000</v>
+        <v>4794000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4759 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №271/26 от 11.08.2026</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>26400000</v>
+        <v>37936000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>1919000</v>
+        <v>3903000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Navro'z Non MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>395841375</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000680321059001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8160 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №187/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>28319000</v>
+        <v>41839000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46237</v>
+        <v>46245</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
-      <c r="C84" s="2" t="n">
-        <v>8651000</v>
-      </c>
-      <c r="D84" s="2" t="n"/>
+      <c r="C84" s="2" t="n"/>
+      <c r="D84" s="2" t="n">
+        <v>1811000</v>
+      </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Navoiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>254744906</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000086309617001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №69/26</t>
+          <t>Оплата по с/ф №7891 за поставленный товар</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>19668000</v>
+        <v>43650000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>7428000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>2177000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №692 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №221/26</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>27096000</v>
+        <v>41473000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n"/>
       <c r="D86" s="2" t="n">
-        <v>3203000</v>
+        <v>9527000</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
+          <t>Оплата за продукцию по договору №107/26, НДС 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>30299000</v>
+        <v>51000000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>3031000</v>
+        <v>16891000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Nurafshon Sut MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>330950664</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000206012374001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1179 за поставленный товар</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTN. №127/26, QQS 12%</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>33330000</v>
+        <v>67891000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46239</v>
+        <v>46248</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
       <c r="C88" s="2" t="n"/>
       <c r="D88" s="2" t="n">
-        <v>1866000</v>
+        <v>1710000</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>370754710</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000693120780001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1458 за поставленный товар</t>
+          <t>Предоплата за товар по договору №110/26 от 14.08.2026</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>35196000</v>
+        <v>69601000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46239</v>
+        <v>46251</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n">
-        <v>11805000</v>
-      </c>
-      <c r="D89" s="2" t="n"/>
+      <c r="C89" s="2" t="n"/>
+      <c r="D89" s="2" t="n">
+        <v>2716000</v>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Sharq Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Заработная плата за июль 2026 г. (перечисление на пластиковые карты)</t>
+          <t>Оплата по счет-фактуре №7900 за поставленный товар</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>23391000</v>
+        <v>72317000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
-      <c r="C90" s="2" t="n">
-        <v>8427000</v>
-      </c>
-      <c r="D90" s="2" t="n"/>
+      <c r="C90" s="2" t="n"/>
+      <c r="D90" s="2" t="n">
+        <v>826000</v>
+      </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №5371</t>
+          <t>Оплата за продукцию по договору №236/26, НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>14964000</v>
+        <v>73143000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>4537000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №64/26 от 07.08.2026</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>19501000</v>
+        <v>71533000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>4365000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>1610000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>249958413</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000576803210001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Shartnoma №234/26 bo'yicha oldindan to'lov</t>
+          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>23866000</v>
+        <v>69923000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>2208000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>1971000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №64/26, НДС 12%</t>
+          <t>Оплата за сырье по дог. №83/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>26074000</v>
+        <v>67952000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46241</v>
+        <v>46251</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>1193000</v>
+        <v>15426000</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Andijon Agro MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>389270245</t>
+          <t>261711878</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000515169628001</t>
+          <t>20208000751559415001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Арендная плата за август 2026 г. по дог. №85/23</t>
+          <t>Оплата за сырье по дог. №3/26 от 17.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>24881000</v>
+        <v>52526000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>9081000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>4848000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №291/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3246 18.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>15800000</v>
+        <v>57374000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46241</v>
+        <v>46252</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>16025000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>3269000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №153/26</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №8892 ОТ 18.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>-225000</v>
+        <v>60643000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>3943000</v>
+        <v>2877000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №955 за поставленный товар</t>
+          <t>Оплата з продукцию по договору №224/26, НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>3718000</v>
+        <v>63520000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>1799000</v>
+        <v>2068000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №176/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №70/26 от 18.08.2026</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>5517000</v>
+        <v>65588000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>1278000</v>
+        <v>2010000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №79/26 от 10.08.2026</t>
+          <t>Оплата за товар по с/ф №269 от 18.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>6795000</v>
+        <v>67598000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>2504000</v>
+        <v>1642000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №350</t>
+          <t>Оплата за товар по счет-фактуре №9733 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>9299000</v>
+        <v>69240000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
-      <c r="C101" s="2" t="n">
-        <v>11315000</v>
-      </c>
-      <c r="D101" s="2" t="n"/>
+      <c r="C101" s="2" t="n"/>
+      <c r="D101" s="2" t="n">
+        <v>1619000</v>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №85/26, QQS BILAN</t>
+          <t>Оплата по счет-фактуре №6913 за поставленный товар</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>-2016000</v>
+        <v>70859000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n">
-        <v>8000000</v>
+        <v>1037000</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5889 за поставленный товар</t>
+          <t>Оплата за товар по счет-фактуре №4899 от 19.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>5984000</v>
+        <v>71896000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46246</v>
+        <v>46253</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>7413000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>7511000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2626 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за материалы по договору №21/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>13397000</v>
+        <v>64385000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46248</v>
+        <v>46254</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n">
-        <v>6101000</v>
-      </c>
+      <c r="C104" s="2" t="n">
+        <v>48506000</v>
+      </c>
+      <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5537 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №294/26</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>19498000</v>
+        <v>15879000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46248</v>
+        <v>46255</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>4084000</v>
+        <v>5941000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Оплата затовар по счет-фактуре №895 от 14.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2211 от 21.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>23582000</v>
+        <v>21820000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n"/>
       <c r="D106" s="2" t="n">
-        <v>2183000</v>
+        <v>4209000</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №37/26 от 17.08.2026</t>
+          <t>Оплата за товар по с/ф №7452 от 21.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>25765000</v>
+        <v>26029000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>1610000</v>
+        <v>11451000</v>
       </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Toshkent Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>365398622</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000416945662001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Iyul oyi uchun ijtimoiy soliq</t>
+          <t>Предоплата за материалы по договору №36/26</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>24155000</v>
+        <v>14578000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
-      <c r="C108" s="2" t="n">
-        <v>1610000</v>
-      </c>
-      <c r="D108" s="2" t="n"/>
+      <c r="C108" s="2" t="n"/>
+      <c r="D108" s="2" t="n">
+        <v>2702000</v>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Jismoniy shaxslar daromad solig'i iyul 2026</t>
+          <t>Предоплата за товар по договору №71/26 от 24.08.2026</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>22545000</v>
+        <v>17280000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
-      <c r="C109" s="2" t="n">
-        <v>6316000</v>
-      </c>
-      <c r="D109" s="2" t="n"/>
+      <c r="C109" s="2" t="n"/>
+      <c r="D109" s="2" t="n">
+        <v>2018000</v>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ziyo Avto Savdo MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>381351815</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000834991110001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №7709</t>
+          <t>Оплата по счет-фактуре №901 за поставленный товар</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>16229000</v>
+        <v>19298000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>9074000</v>
+        <v>1368000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Termiz Avto Savdo AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>210971141</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000648382170001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №270/26 от 17.08.2026, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №9806</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>7155000</v>
+        <v>17930000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>9215000</v>
+        <v>1933000</v>
       </c>
       <c r="D111" s="2" t="n"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>390109711</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000116483821001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №187/26</t>
+          <t>Уплата налога на добавленную стоимость за июль</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>-2060000</v>
+        <v>15997000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
-      <c r="C112" s="2" t="n">
-        <v>17271000</v>
-      </c>
-      <c r="D112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n">
+        <v>1177000</v>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Saodat Dori-Darmon XK</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>214547449</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000670863096001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №4309</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2486 25.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>-19331000</v>
+        <v>17174000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46251</v>
+        <v>46259</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>19018000</v>
+        <v>15400000</v>
       </c>
       <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>364967255</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-6825)</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>16307000257461212417</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №250/26, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-6825 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>-38349000</v>
+        <v>1774000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46252</v>
+        <v>46260</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n"/>
       <c r="D114" s="2" t="n">
-        <v>2289000</v>
+        <v>4523000</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №104/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2047 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>-36060000</v>
+        <v>6297000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
       <c r="C115" s="2" t="n"/>
       <c r="D115" s="2" t="n">
-        <v>7496000</v>
+        <v>3359000</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>249958413</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000576803210001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №67/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4526 от 26.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>-28564000</v>
+        <v>9656000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>1469000</v>
+        <v>3136000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Navoiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>254744906</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000086309617001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №16/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5250 26.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>-27095000</v>
+        <v>12792000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46253</v>
+        <v>46260</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n">
-        <v>9075000</v>
-      </c>
-      <c r="D117" s="2" t="n"/>
+      <c r="C117" s="2" t="n"/>
+      <c r="D117" s="2" t="n">
+        <v>1412000</v>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4906,37 +4901,37 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №299/26</t>
+          <t>Оплата за продукцию по договору №81/26, НДС 12%</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>-36170000</v>
+        <v>14204000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46254</v>
+        <v>46260</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n"/>
-      <c r="D118" s="2" t="n">
-        <v>2859000</v>
-      </c>
+      <c r="C118" s="2" t="n">
+        <v>9121000</v>
+      </c>
+      <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Farovon Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>268551631</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000220509016001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4946,117 +4941,117 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №188/26, НДС 12%</t>
+          <t>Предоплата за материалы по договору №119/26</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>-33311000</v>
+        <v>5083000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46254</v>
+        <v>46261</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>4840000</v>
+        <v>746000</v>
       </c>
       <c r="D119" s="2" t="n"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000005529105001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №294/26</t>
+          <t>Оплата за электроэнергию за август 2026 г.</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>-38151000</v>
+        <v>4337000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46255</v>
+        <v>46261</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
-      <c r="C120" s="2" t="n"/>
-      <c r="D120" s="2" t="n">
-        <v>5475000</v>
-      </c>
+      <c r="C120" s="2" t="n">
+        <v>1335000</v>
+      </c>
+      <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tong Non MChJ</t>
+          <t>Andijon Agro MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>355228810</t>
+          <t>261711878</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000706960004001</t>
+          <t>20208000751559415001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №221/26 от 21.08.2026</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №104/26 ОТ 27.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>-32676000</v>
+        <v>3002000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46255</v>
+        <v>46262</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
-      <c r="C121" s="2" t="n">
-        <v>3053000</v>
-      </c>
-      <c r="D121" s="2" t="n"/>
+      <c r="C121" s="2" t="n"/>
+      <c r="D121" s="2" t="n">
+        <v>7623000</v>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jizzax Un Mahsulotlari MChJ</t>
+          <t>Namangan Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>346612418</t>
+          <t>275471006</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000418784476001</t>
+          <t>20208000312078083001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -5066,117 +5061,117 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №121/26</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №198/26, НДС 12%</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>-35729000</v>
+        <v>10625000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>27473000</v>
+        <v>20732000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №119/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №7604 за поставленный товар</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>-8256000</v>
+        <v>31357000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
       <c r="C123" s="2" t="n"/>
       <c r="D123" s="2" t="n">
-        <v>3198000</v>
+        <v>3554000</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2763</t>
+          <t>Оплата по счет-фактуре №8590 за поставленный товар</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>-5058000</v>
+        <v>34911000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>2913000</v>
+        <v>1478000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5186,232 +5181,232 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №7186 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за продуцию по договору №7/26, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>-2145000</v>
+        <v>36389000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>1820000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>285545487</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7947 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>ПЛАТА ЗА SMS-ИНФОРМИРОВАНИЕ</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>-325000</v>
+        <v>36089000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>2006000</v>
+        <v>14688000</v>
       </c>
       <c r="D126" s="2" t="n"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Andijon Agro MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>261711878</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000751559415001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Оплата за товары согласно /ф №5703</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>-2331000</v>
+        <v>21401000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n"/>
-      <c r="D127" s="2" t="n">
-        <v>6433000</v>
-      </c>
+      <c r="C127" s="2" t="n">
+        <v>4746000</v>
+      </c>
+      <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9188 25.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №142/26</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>4102000</v>
+        <v>16655000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46259</v>
+        <v>46267</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
-      <c r="C128" s="2" t="n"/>
-      <c r="D128" s="2" t="n">
-        <v>1614000</v>
-      </c>
+      <c r="C128" s="2" t="n">
+        <v>65757000</v>
+      </c>
+      <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №127/26 от 25.08.2026</t>
+          <t>Оплата за товары согласно с/ф №300</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>5716000</v>
+        <v>-49102000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46259</v>
+        <v>46269</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>15400000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>14902000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-6825)</t>
+          <t>Angren Meva-Sabzavot XK</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>16307000257461212417</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-6825 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за товар по договору №130/26 от 04.09.2026</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>-9684000</v>
+        <v>-34200000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46261</v>
+        <v>46269</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>7703000</v>
+        <v>11241000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5421,197 +5416,192 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №1/26 от 27.08.2026</t>
+          <t>Предоплата за товар по договору №246/26 от 04.09.2026</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>-1981000</v>
+        <v>-22959000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46261</v>
+        <v>46269</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>3373000</v>
+        <v>790000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №444 за поставленный товар</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4926 ОТ 04.09.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1392000</v>
+        <v>-22169000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46261</v>
+        <v>46269</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>746000</v>
+        <v>5715000</v>
       </c>
       <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000709052368001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за август 2026 г.</t>
+          <t>Оплата за сырье по договору №267/26 от 04.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>646000</v>
+        <v>-27884000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>12819000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>11847000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>285545487</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1361</t>
+          <t>Перечисление заработной платы за август 2026 г. согласно реестру №6736</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>13465000</v>
+        <v>-39731000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
       <c r="C134" s="2" t="n"/>
       <c r="D134" s="2" t="n">
-        <v>3723000</v>
+        <v>6194000</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>249958413</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000576803210001</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9130 за поставленный товар</t>
+          <t>Shartnoma №61/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>17188000</v>
+        <v>-33537000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
       <c r="C135" s="2" t="n"/>
       <c r="D135" s="2" t="n">
-        <v>3120000</v>
+        <v>2430000</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5621,272 +5611,277 @@
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №61 от 31.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №39/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>20308000</v>
+        <v>-31107000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D136" s="2" t="n"/>
+      <c r="C136" s="2" t="n"/>
+      <c r="D136" s="2" t="n">
+        <v>1105000</v>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Sharq Polimer MChJ</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>ПЛАТА ЗА SMS-ИНФОРМИРОВАНИЕ</t>
+          <t>Оплата за товар по счет-фактуре №2673 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>20008000</v>
+        <v>-30002000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
-      <c r="C137" s="2" t="n">
-        <v>4696000</v>
-      </c>
-      <c r="D137" s="2" t="n"/>
+      <c r="C137" s="2" t="n"/>
+      <c r="D137" s="2" t="n">
+        <v>1044000</v>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №142/26</t>
+          <t>Предоплата за товар по договору №291/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>15312000</v>
+        <v>-28958000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46267</v>
+        <v>46272</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
-      <c r="C138" s="2" t="n">
-        <v>65062000</v>
-      </c>
-      <c r="D138" s="2" t="n"/>
+      <c r="C138" s="2" t="n"/>
+      <c r="D138" s="2" t="n">
+        <v>744000</v>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Navoiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>254744906</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000086309617001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №300</t>
+          <t>Оплата по счет-фактуре №3581 за поставленный товар</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>-49750000</v>
+        <v>-28214000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>14902000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>6979000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Zafar Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>235181568</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000499111061001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №130/26 от 04.09.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №2321</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>-34848000</v>
+        <v>-35193000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
-      <c r="C140" s="2" t="n"/>
-      <c r="D140" s="2" t="n">
-        <v>11241000</v>
-      </c>
+      <c r="C140" s="2" t="n">
+        <v>14036000</v>
+      </c>
+      <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Toshkent Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>365398622</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000416945662001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №246/26 от 04.09.2026</t>
+          <t>Оплата за транспортные услуги по договору №285/26</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>-23607000</v>
+        <v>-49229000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
       <c r="C141" s="2" t="n"/>
       <c r="D141" s="2" t="n">
-        <v>790000</v>
+        <v>667000</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №4926 ОТ 04.09.2026, В Т.Ч. НДС 12%</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8023 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>-22817000</v>
+        <v>-48562000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>5655000</v>
+        <v>1198000</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Shahrisabz Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>387683548</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000759953911001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -5896,672 +5891,677 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №267/26 от 04.09.2026, НДС 12%</t>
+          <t>Аренда помещения за сентябрь, дог. №51/25</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>-28472000</v>
+        <v>-49760000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>11847000</v>
+        <v>11046000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Sarbon Moliya Bank</t>
+          <t>Oqtosh Trans Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №6736</t>
+          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №3151</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>-40319000</v>
+        <v>-60806000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n"/>
       <c r="D144" s="2" t="n">
-        <v>6194000</v>
+        <v>457000</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Shartnoma №61/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата по счет-фактуре №2113 за поставленный товар</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>-34125000</v>
+        <v>-60349000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>2430000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>4262000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Andijon Agro MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>261711878</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000751559415001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №39/26 от 07.09.2026</t>
+          <t>Предоплата за материалы по договору №72/26</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>-31695000</v>
+        <v>-64611000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n"/>
       <c r="D146" s="2" t="n">
-        <v>1105000</v>
+        <v>1010000</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2673 от 07.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №3882 от 10.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>-30590000</v>
+        <v>-63601000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>1044000</v>
+        <v>387000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №291/26 от 07.09.2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №132/26, QQS 12%</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>-29546000</v>
+        <v>-63214000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>744000</v>
+        <v>5196000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Tong Non MChJ</t>
+          <t>Namangan Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>355228810</t>
+          <t>275471006</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000706960004001</t>
+          <t>20208000312078083001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3581 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №22/26, НДС 12%</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>-28802000</v>
+        <v>-58018000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n">
-        <v>6906000</v>
-      </c>
-      <c r="D149" s="2" t="n"/>
+      <c r="C149" s="2" t="n"/>
+      <c r="D149" s="2" t="n">
+        <v>2255000</v>
+      </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Afrosiyob Yog'och XK</t>
+          <t>Navro'z Mebel MChJ</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>390109711</t>
+          <t>296856123</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000116483821001</t>
+          <t>20208000920559413001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №2321</t>
+          <t>Оплата за продукцию по договору №252/26, НДС 12%</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>-35708000</v>
+        <v>-55763000</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="3" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B150" t="n">
         <v>242</v>
       </c>
-      <c r="C150" s="2" t="n">
-        <v>13889000</v>
-      </c>
-      <c r="D150" s="2" t="n"/>
+      <c r="C150" s="2" t="n"/>
+      <c r="D150" s="2" t="n">
+        <v>24580000</v>
+      </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Saodat Moy MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>323617118</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>20208000897515594001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №285/26</t>
+          <t>Оплата по с/ф №6158 за поставленный товар</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>-49597000</v>
+        <v>-31183000</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="3" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="B151" t="n">
         <v>243</v>
       </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>667000</v>
-      </c>
+      <c r="C151" s="2" t="n">
+        <v>1615000</v>
+      </c>
+      <c r="D151" s="2" t="n"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №8023 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Уплата социального налога за август</t>
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>-48930000</v>
+        <v>-32798000</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="3" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="B152" t="n">
         <v>244</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>1198000</v>
+        <v>1615000</v>
       </c>
       <c r="D152" s="2" t="n"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Termiz Qurilish MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>389270245</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>20208000515169628001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №85/23</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>-50128000</v>
+        <v>-34413000</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="3" t="n">
-        <v>46273</v>
+        <v>46281</v>
       </c>
       <c r="B153" t="n">
         <v>245</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>10930000</v>
+        <v>6089000</v>
       </c>
       <c r="D153" s="2" t="n"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО СЧЕТ-ФАКТУРЕ №3151</t>
+          <t>Оплата за сырье по договору №249/26 от 16.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>-61058000</v>
+        <v>-40502000</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="3" t="n">
-        <v>46274</v>
+        <v>46282</v>
       </c>
       <c r="B154" t="n">
         <v>246</v>
       </c>
       <c r="C154" s="2" t="n"/>
       <c r="D154" s="2" t="n">
-        <v>457000</v>
+        <v>38889000</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №2113 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №5529 за поставленный товар</t>
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>-60601000</v>
+        <v>-1613000</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="3" t="n">
-        <v>46274</v>
+        <v>46282</v>
       </c>
       <c r="B155" t="n">
         <v>247</v>
       </c>
-      <c r="C155" s="2" t="n">
-        <v>4217000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
+      <c r="C155" s="2" t="n"/>
+      <c r="D155" s="2" t="n">
+        <v>15071000</v>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Saodat Dori-Darmon XK</t>
+          <t>Navro'z Non MChJ</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>214547449</t>
+          <t>395841375</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>20208000670863096001</t>
+          <t>20208000680321059001</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №72/26</t>
+          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>-64818000</v>
+        <v>13458000</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="3" t="n">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="B156" t="n">
         <v>248</v>
       </c>
       <c r="C156" s="2" t="n"/>
       <c r="D156" s="2" t="n">
-        <v>1010000</v>
+        <v>2946000</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3882 от 10.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6728 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>-63808000</v>
+        <v>16404000</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="3" t="n">
-        <v>46275</v>
+        <v>46286</v>
       </c>
       <c r="B157" t="n">
         <v>249</v>
       </c>
       <c r="C157" s="2" t="n"/>
       <c r="D157" s="2" t="n">
-        <v>387000</v>
+        <v>1613000</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartn. №132/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №239/26, НДС 12%</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>-63421000</v>
+        <v>18017000</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B158" t="n">
         <v>250</v>
       </c>
       <c r="C158" s="2" t="n"/>
       <c r="D158" s="2" t="n">
-        <v>5196000</v>
+        <v>732000</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Bekobod Agro Servis MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>370754710</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>20208000693120780001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №22/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №530 за поставленный товар</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>-58225000</v>
+        <v>18749000</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B159" t="n">
         <v>251</v>
       </c>
       <c r="C159" s="2" t="n"/>
       <c r="D159" s="2" t="n">
-        <v>2255000</v>
+        <v>402000</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Gulshan Meva Eksport MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>223968561</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>20208000359205594001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -6571,157 +6571,157 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №252/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №4376 от 21.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>-55970000</v>
+        <v>19151000</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="n">
-        <v>46280</v>
+        <v>46286</v>
       </c>
       <c r="B160" t="n">
         <v>252</v>
       </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>24580000</v>
-      </c>
+      <c r="C160" s="2" t="n">
+        <v>1991000</v>
+      </c>
+      <c r="D160" s="2" t="n"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №6158 за поставленный товар</t>
+          <t>НДС за август 2026 г.</t>
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>-31390000</v>
+        <v>17160000</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="3" t="n">
-        <v>46281</v>
+        <v>46287</v>
       </c>
       <c r="B161" t="n">
         <v>253</v>
       </c>
-      <c r="C161" s="2" t="n">
-        <v>1615000</v>
-      </c>
-      <c r="D161" s="2" t="n"/>
+      <c r="C161" s="2" t="n"/>
+      <c r="D161" s="2" t="n">
+        <v>6639000</v>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Yog' Zavodi MChJ</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>254744906</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000086309617001</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1260 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>-33005000</v>
+        <v>23799000</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B162" t="n">
         <v>254</v>
       </c>
-      <c r="C162" s="2" t="n">
-        <v>1615000</v>
-      </c>
-      <c r="D162" s="2" t="n"/>
+      <c r="C162" s="2" t="n"/>
+      <c r="D162" s="2" t="n">
+        <v>6601000</v>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Оплата по с/ф №1600 за поставленный товар</t>
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>-34620000</v>
+        <v>30400000</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="3" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="B163" t="n">
         <v>255</v>
       </c>
-      <c r="C163" s="2" t="n">
-        <v>6025000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
+      <c r="C163" s="2" t="n"/>
+      <c r="D163" s="2" t="n">
+        <v>1760000</v>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Buxoro Sut AJ</t>
+          <t>Chust Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>364967255</t>
+          <t>354548714</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>20208000405131305001</t>
+          <t>20208000537910113001</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -6731,77 +6731,77 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №249/26 от 16.09.2026, НДС 12%</t>
+          <t>Предоплата за товар по договору №24/26 от 23.09.2026</t>
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>-40645000</v>
+        <v>32160000</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="3" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B164" t="n">
         <v>256</v>
       </c>
       <c r="C164" s="2" t="n"/>
       <c r="D164" s="2" t="n">
-        <v>38889000</v>
+        <v>831000</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Namangan Oziq-ovqat Savdo MChJ</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>232722302</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000251961831001</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5529 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4711</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>-1756000</v>
+        <v>32991000</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="3" t="n">
-        <v>46282</v>
+        <v>46288</v>
       </c>
       <c r="B165" t="n">
         <v>257</v>
       </c>
       <c r="C165" s="2" t="n"/>
       <c r="D165" s="2" t="n">
-        <v>15071000</v>
+        <v>800000</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Navro'z Non MChJ</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>249958413</t>
+          <t>395841375</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>20208000576803210001</t>
+          <t>20208000680321059001</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -6811,672 +6811,667 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Shartnoma №173/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>13315000</v>
+        <v>33791000</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B166" t="n">
         <v>258</v>
       </c>
       <c r="C166" s="2" t="n"/>
       <c r="D166" s="2" t="n">
-        <v>2946000</v>
+        <v>726000</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6728 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №35/26 от 23.09.2026</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>16261000</v>
+        <v>34517000</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="3" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="B167" t="n">
         <v>259</v>
       </c>
       <c r="C167" s="2" t="n"/>
       <c r="D167" s="2" t="n">
-        <v>1613000</v>
+        <v>400000</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №239/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №5977 за поставленный товар</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>17874000</v>
+        <v>34917000</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="3" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="B168" t="n">
         <v>260</v>
       </c>
       <c r="C168" s="2" t="n"/>
       <c r="D168" s="2" t="n">
-        <v>732000</v>
+        <v>1820000</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №530 за поставленный товар</t>
+          <t>Оплата по счет-фактуре №8460 за поставленный товар</t>
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>18606000</v>
+        <v>36737000</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="3" t="n">
-        <v>46286</v>
+        <v>46289</v>
       </c>
       <c r="B169" t="n">
         <v>261</v>
       </c>
       <c r="C169" s="2" t="n"/>
       <c r="D169" s="2" t="n">
-        <v>402000</v>
+        <v>656000</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4376 от 21.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6522 от 24.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>19008000</v>
+        <v>37393000</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="3" t="n">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="B170" t="n">
         <v>262</v>
       </c>
-      <c r="C170" s="2" t="n">
-        <v>1991000</v>
-      </c>
-      <c r="D170" s="2" t="n"/>
+      <c r="C170" s="2" t="n"/>
+      <c r="D170" s="2" t="n">
+        <v>1181000</v>
+      </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>Оплата за товар по счет-фактуре №7510 от 25.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>17017000</v>
+        <v>38574000</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="3" t="n">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="B171" t="n">
         <v>263</v>
       </c>
-      <c r="C171" s="2" t="n"/>
-      <c r="D171" s="2" t="n">
-        <v>6639000</v>
-      </c>
+      <c r="C171" s="2" t="n">
+        <v>3980000</v>
+      </c>
+      <c r="D171" s="2" t="n"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Tong Non MChJ</t>
+          <t>Andijon Agro MChJ</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>355228810</t>
+          <t>261711878</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>20208000706960004001</t>
+          <t>20208000751559415001</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №1260 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Предоплата за материалы по доовору №151/26</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>23656000</v>
+        <v>34594000</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="3" t="n">
-        <v>46288</v>
+        <v>46290</v>
       </c>
       <c r="B172" t="n">
         <v>264</v>
       </c>
-      <c r="C172" s="2" t="n"/>
-      <c r="D172" s="2" t="n">
-        <v>6601000</v>
-      </c>
+      <c r="C172" s="2" t="n">
+        <v>15400000</v>
+      </c>
+      <c r="D172" s="2" t="n"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>379461924</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-6825)</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>16307000257461212417</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №1600 за поставленный товар</t>
+          <t>Kredit shartnomasi L-2025-6825 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>30257000</v>
+        <v>19194000</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B173" t="n">
         <v>265</v>
       </c>
       <c r="C173" s="2" t="n"/>
       <c r="D173" s="2" t="n">
-        <v>1760000</v>
+        <v>1264000</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Ilhom Qog'oz AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>285545487</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>20208000455379101001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №24/26 от 23.09.2026</t>
+          <t>Предоплата за товар по договору №174/26 от 28.09.2026</t>
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>32017000</v>
+        <v>20458000</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B174" t="n">
         <v>266</v>
       </c>
       <c r="C174" s="2" t="n"/>
       <c r="D174" s="2" t="n">
-        <v>831000</v>
+        <v>402000</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Oydin Yog' Zavodi MChJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>353327223</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>20208000282519618001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4711</t>
+          <t>Оплата по счет-фактуре №4059 за поставленный товар</t>
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>32848000</v>
+        <v>20860000</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B175" t="n">
         <v>267</v>
       </c>
-      <c r="C175" s="2" t="n"/>
-      <c r="D175" s="2" t="n">
-        <v>800000</v>
-      </c>
+      <c r="C175" s="2" t="n">
+        <v>748000</v>
+      </c>
+      <c r="D175" s="2" t="n"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Zafar Non MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>249958413</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>20208000576803210001</t>
+          <t>20208000005529105001</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>33648000</v>
+        <v>20112000</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="3" t="n">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B176" t="n">
         <v>268</v>
       </c>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n">
-        <v>726000</v>
-      </c>
+      <c r="C176" s="2" t="n">
+        <v>7172000</v>
+      </c>
+      <c r="D176" s="2" t="n"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №35/26 от 23.09.2026</t>
+          <t>Оплата за товары согласно счет-фактуре №7219</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>34374000</v>
+        <v>12940000</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="3" t="n">
-        <v>46288</v>
+        <v>46294</v>
       </c>
       <c r="B177" t="n">
         <v>269</v>
       </c>
       <c r="C177" s="2" t="n"/>
       <c r="D177" s="2" t="n">
-        <v>400000</v>
+        <v>6082000</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Navro'z Non MChJ</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>395841375</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000680321059001</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5977 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>34774000</v>
+        <v>19022000</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="3" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="B178" t="n">
         <v>270</v>
       </c>
       <c r="C178" s="2" t="n"/>
       <c r="D178" s="2" t="n">
-        <v>1820000</v>
+        <v>2425000</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8460 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>36594000</v>
+        <v>21447000</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="3" t="n">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="B179" t="n">
         <v>271</v>
       </c>
-      <c r="C179" s="2" t="n"/>
-      <c r="D179" s="2" t="n">
-        <v>656000</v>
-      </c>
+      <c r="C179" s="2" t="n">
+        <v>2587000</v>
+      </c>
+      <c r="D179" s="2" t="n"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>379461924</t>
+          <t>361241894</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>20208000126427211001</t>
+          <t>20208000878447683001</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №6522 от 24.09.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №157/26 от 29.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>37250000</v>
+        <v>18860000</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="3" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B180" t="n">
         <v>272</v>
       </c>
       <c r="C180" s="2" t="n"/>
       <c r="D180" s="2" t="n">
-        <v>1181000</v>
+        <v>863000</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Barakali Logistik MChJ</t>
+          <t>Sharq Polimer MChJ</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>346293251</t>
+          <t>329325198</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>20208000836795443001</t>
+          <t>20208000679544394001</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №7510 от 25.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3813 30.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>38431000</v>
+        <v>19723000</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="3" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B181" t="n">
         <v>273</v>
       </c>
-      <c r="C181" s="2" t="n">
-        <v>3939000</v>
-      </c>
-      <c r="D181" s="2" t="n"/>
+      <c r="C181" s="2" t="n"/>
+      <c r="D181" s="2" t="n">
+        <v>777000</v>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Saodat Dori-Darmon XK</t>
+          <t>Angren Meva-Sabzavot XK</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>214547449</t>
+          <t>346192451</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>20208000670863096001</t>
+          <t>20208000642721171001</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по доовору №151/26</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9928 30.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>34492000</v>
+        <v>20500000</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="3" t="n">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B182" t="n">
         <v>274</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>15400000</v>
+        <v>300000</v>
       </c>
       <c r="D182" s="2" t="n"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-6825)</t>
+          <t>Sarbon Moliya Bank</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>16307000257461212417</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -7486,431 +7481,36 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-6825 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Плата за SMS-информирование</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>19092000</v>
+        <v>20200000</v>
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B183" t="n">
-        <v>275</v>
-      </c>
-      <c r="C183" s="2" t="n"/>
-      <c r="D183" s="2" t="n">
-        <v>1264000</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>379461924</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>20208000126427211001</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I183" t="inlineStr">
-        <is>
-          <t>Предоплата за товар по договору №174/26 от 28.09.2026</t>
-        </is>
-      </c>
-      <c r="J183" s="2" t="n">
-        <v>20356000</v>
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="n">
+        <v>489435000</v>
+      </c>
+      <c r="D183" s="4" t="n">
+        <v>479935000</v>
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B184" t="n">
-        <v>276</v>
-      </c>
-      <c r="C184" s="2" t="n"/>
-      <c r="D184" s="2" t="n">
-        <v>402000</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>379461924</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>20208000126427211001</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Оплата по счет-фактуре №4059 за поставленный товар</t>
-        </is>
-      </c>
-      <c r="J184" s="2" t="n">
-        <v>20758000</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B185" t="n">
-        <v>277</v>
-      </c>
-      <c r="C185" s="2" t="n">
-        <v>748000</v>
-      </c>
-      <c r="D185" s="2" t="n"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>20208000709052368001</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>Оплата за электроэнергию согласно счету</t>
-        </is>
-      </c>
-      <c r="J185" s="2" t="n">
-        <v>20010000</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B186" t="n">
-        <v>278</v>
-      </c>
-      <c r="C186" s="2" t="n">
-        <v>7097000</v>
-      </c>
-      <c r="D186" s="2" t="n"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Buxoro Sut AJ</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>364967255</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>20208000405131305001</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>Оплата за товары согласно счет-фактуре №7219</t>
-        </is>
-      </c>
-      <c r="J186" s="2" t="n">
-        <v>12913000</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B187" t="n">
-        <v>279</v>
-      </c>
-      <c r="C187" s="2" t="n"/>
-      <c r="D187" s="2" t="n">
-        <v>6082000</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Zafar Non MChJ</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>249958413</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>20208000576803210001</t>
-        </is>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I187" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №275/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="n">
-        <v>18995000</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B188" t="n">
-        <v>280</v>
-      </c>
-      <c r="C188" s="2" t="n"/>
-      <c r="D188" s="2" t="n">
-        <v>2425000</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>379461924</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>20208000126427211001</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>Оплата за продукцию по договору №210/26, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J188" s="2" t="n">
-        <v>21420000</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="n">
-        <v>46294</v>
-      </c>
-      <c r="B189" t="n">
-        <v>281</v>
-      </c>
-      <c r="C189" s="2" t="n">
-        <v>2560000</v>
-      </c>
-      <c r="D189" s="2" t="n"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>Buxoro Sut AJ</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>364967255</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>20208000405131305001</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Оплата за сырье по договору №157/26 от 29.09.2026, НДС 12%</t>
-        </is>
-      </c>
-      <c r="J189" s="2" t="n">
-        <v>18860000</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B190" t="n">
-        <v>282</v>
-      </c>
-      <c r="C190" s="2" t="n"/>
-      <c r="D190" s="2" t="n">
-        <v>863000</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>Barakali Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>346293251</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>20208000836795443001</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3813 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J190" s="2" t="n">
-        <v>19723000</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B191" t="n">
-        <v>283</v>
-      </c>
-      <c r="C191" s="2" t="n"/>
-      <c r="D191" s="2" t="n">
-        <v>777000</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>Shahrisabz Mehmonxona AJ</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>379461924</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>20208000126427211001</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9928 30.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J191" s="2" t="n">
-        <v>20500000</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B192" t="n">
-        <v>284</v>
-      </c>
-      <c r="C192" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D192" s="2" t="n"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>Sarbon Moliya Bank</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I192" t="inlineStr">
-        <is>
-          <t>Плата за SMS-информирование</t>
-        </is>
-      </c>
-      <c r="J192" s="2" t="n">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="n">
         <v>20200000</v>
       </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C193" s="4" t="n">
-        <v>485321000</v>
-      </c>
-      <c r="D193" s="4" t="n">
-        <v>475821000</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C194" s="4" t="n">
-        <v>20200000</v>
-      </c>
-      <c r="D194" s="4" t="n"/>
+      <c r="D184" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
